--- a/docs/PageBinder-feature-comparison.xlsx
+++ b/docs/PageBinder-feature-comparison.xlsx
@@ -877,7 +877,7 @@
     <t xml:space="preserve">Searches inside attachments</t>
   </si>
   <si>
-    <t xml:space="preserve">Partial: text of saved emails</t>
+    <t xml:space="preserve">Partial: saved emails and PDF printouts (not plain attachments)</t>
   </si>
   <si>
     <t xml:space="preserve">Yes: OCR of images and PDFs *</t>
@@ -6391,7 +6391,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="19" t="s">
         <v>282</v>
       </c>
